--- a/data/trans_camb/P7_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P7_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 6,87</t>
+          <t>-1,38; 7,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 5,0</t>
+          <t>-3,52; 5,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 12,09</t>
+          <t>2,71; 12,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 1,11</t>
+          <t>-6,47; 1,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 0,39</t>
+          <t>-8,23; 0,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 6,68</t>
+          <t>-1,24; 6,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,64</t>
+          <t>-2,97; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,46</t>
+          <t>-4,92; 1,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 8,34</t>
+          <t>1,85; 8,31</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 22,93</t>
+          <t>-3,63; 23,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 16,12</t>
+          <t>-10,43; 17,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 40,05</t>
+          <t>7,85; 41,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 2,53</t>
+          <t>-12,6; 2,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 0,91</t>
+          <t>-16,23; 0,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 13,94</t>
+          <t>-2,32; 14,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 6,55</t>
+          <t>-6,86; 7,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 3,63</t>
+          <t>-11,34; 3,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 20,38</t>
+          <t>4,29; 20,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,18</t>
+          <t>0,25; 4,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,47</t>
+          <t>2,29; 6,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 7,43</t>
+          <t>0,67; 7,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,05</t>
+          <t>-1,9; 3,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,93</t>
+          <t>-0,99; 4,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 3,16</t>
+          <t>-4,32; 3,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,87</t>
+          <t>-0,23; 2,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,38</t>
+          <t>1,27; 4,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,91</t>
+          <t>-0,31; 4,86</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 61,27</t>
+          <t>2,57; 58,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,27; 91,85</t>
+          <t>25,28; 86,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,27; 102,19</t>
+          <t>9,06; 102,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 21,13</t>
+          <t>-11,61; 23,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 27,56</t>
+          <t>-5,8; 27,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 21,13</t>
+          <t>-25,88; 22,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 26,12</t>
+          <t>-2,25; 26,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 41,18</t>
+          <t>10,25; 42,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 43,88</t>
+          <t>-2,25; 43,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 1,86</t>
+          <t>-5,62; 1,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 0,62</t>
+          <t>-5,96; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,42</t>
+          <t>-1,23; 5,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,87; -2,46</t>
+          <t>-10,68; -2,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,36; -0,06</t>
+          <t>-8,88; -0,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,07; -0,5</t>
+          <t>-7,81; -0,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,69; -1,37</t>
+          <t>-6,97; -1,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -0,71</t>
+          <t>-5,83; -0,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,79</t>
+          <t>-3,06; 2,04</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 27,77</t>
+          <t>-57,73; 34,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 12,09</t>
+          <t>-58,04; 13,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 78,7</t>
+          <t>-11,77; 89,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,05; -18,93</t>
+          <t>-63,92; -17,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,77; -0,85</t>
+          <t>-52,49; -1,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,62; -2,98</t>
+          <t>-45,98; -1,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,77; -13,48</t>
+          <t>-55,52; -14,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,18; -5,94</t>
+          <t>-46,38; -5,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 19,14</t>
+          <t>-23,62; 21,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,79</t>
+          <t>-0,77; 2,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,96</t>
+          <t>-1,7; 1,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 3,16</t>
+          <t>-2,91; 2,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,16</t>
+          <t>-4,33; 0,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,03; -2,52</t>
+          <t>-6,65; -2,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -3,73</t>
+          <t>-10,62; -3,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,85</t>
+          <t>-1,92; 0,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -0,84</t>
+          <t>-3,59; -0,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,24; -0,85</t>
+          <t>-5,38; -0,96</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 19,18</t>
+          <t>-4,43; 20,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 13,6</t>
+          <t>-10,13; 12,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,72; 21,3</t>
+          <t>-18,25; 19,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 0,63</t>
+          <t>-14,38; 0,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,26; -9,23</t>
+          <t>-22,44; -8,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,35; -13,52</t>
+          <t>-35,48; -13,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 3,99</t>
+          <t>-8,25; 4,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,22; -3,93</t>
+          <t>-15,8; -3,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,4; -4,19</t>
+          <t>-24,12; -4,38</t>
         </is>
       </c>
     </row>
